--- a/exports/IDFCFIRSTB_full_report.xlsx
+++ b/exports/IDFCFIRSTB_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q71"/>
+  <dimension ref="A1:U71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>6.39</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44581.55208333334</v>
+        <v>44582.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>47.85</v>
+        <v>47.05</v>
       </c>
       <c r="I2" t="n">
         <v>47.20755784455</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.92</v>
+        <v>-5.52</v>
       </c>
       <c r="L2" t="n">
-        <v>5.42</v>
+        <v>6.02</v>
       </c>
       <c r="M2" t="n">
         <v>0.6</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>6.31</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.55208333334</v>
+        <v>44594.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>47.45</v>
+        <v>48.65</v>
       </c>
       <c r="I3" t="n">
         <v>47.7242800676748</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.85</v>
+        <v>-3.4</v>
       </c>
       <c r="L3" t="n">
-        <v>2.02</v>
+        <v>3.93</v>
       </c>
       <c r="M3" t="n">
         <v>3.11</v>
       </c>
       <c r="N3" t="n">
-        <v>2.43</v>
+        <v>3.9</v>
       </c>
       <c r="O3" t="n">
         <v>-2.19</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>7.65</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44603.55208333334</v>
+        <v>44606.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>46.4</v>
+        <v>44.3</v>
       </c>
       <c r="I4" t="n">
         <v>45.78825566515928</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.62</v>
+        <v>-8.94</v>
       </c>
       <c r="L4" t="n">
-        <v>5.55</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>0.42</v>
+        <v>2.48</v>
       </c>
       <c r="N4" t="n">
-        <v>2.03</v>
+        <v>6.03</v>
       </c>
       <c r="O4" t="n">
         <v>3.9</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>8.49</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44651.55208333334</v>
+        <v>44652.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>39.55</v>
+        <v>41.55</v>
       </c>
       <c r="I5" t="n">
         <v>40.48136922331534</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K5" t="n">
-        <v>10.72</v>
+        <v>6.21</v>
       </c>
       <c r="L5" t="n">
         <v>4.18</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.91</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44669.55208333334</v>
+        <v>44670.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>40.85</v>
+        <v>40.5</v>
       </c>
       <c r="I6" t="n">
         <v>40.52811710768476</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.68</v>
+        <v>-2.53</v>
       </c>
       <c r="L6" t="n">
         <v>5.05</v>
@@ -783,7 +854,7 @@
         <v>0.36</v>
       </c>
       <c r="N6" t="n">
-        <v>1.89</v>
+        <v>2.45</v>
       </c>
       <c r="O6" t="n">
         <v>5.44</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>7.2</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44708.55208333334</v>
+        <v>44711.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>35.45</v>
+        <v>36.4</v>
       </c>
       <c r="I7" t="n">
         <v>36.30659458092969</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K7" t="n">
-        <v>12.47</v>
+        <v>10.12</v>
       </c>
       <c r="L7" t="n">
         <v>1.73</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>8.050000000000001</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44720.55208333334</v>
+        <v>44721.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>34.6</v>
+        <v>34.2</v>
       </c>
       <c r="I8" t="n">
         <v>34.28091801403233</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.95</v>
+        <v>-6.04</v>
       </c>
       <c r="L8" t="n">
-        <v>5.22</v>
+        <v>6.32</v>
       </c>
       <c r="M8" t="n">
         <v>0.43</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,25 +1040,25 @@
         <v>5.94</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44736.55208333334</v>
+        <v>44739.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>30.95</v>
+        <v>32.2</v>
       </c>
       <c r="I9" t="n">
         <v>31.91696771198756</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K9" t="n">
-        <v>9.5</v>
+        <v>5.85</v>
       </c>
       <c r="L9" t="n">
         <v>1.02</v>
       </c>
       <c r="M9" t="n">
-        <v>1.38</v>
+        <v>2.1</v>
       </c>
       <c r="N9" t="n">
         <v>4.03</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10.33</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44826.55208333334</v>
+        <v>44827.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>50.6</v>
+        <v>48.65</v>
       </c>
       <c r="I10" t="n">
         <v>49.48028515698334</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>87.16666666666667</v>
+        <v>88</v>
       </c>
       <c r="K10" t="n">
-        <v>57.14</v>
+        <v>51.09</v>
       </c>
       <c r="L10" t="n">
         <v>4.97</v>
@@ -1011,7 +1130,7 @@
         <v>5.05</v>
       </c>
       <c r="N10" t="n">
-        <v>3.12</v>
+        <v>3.75</v>
       </c>
       <c r="O10" t="n">
         <v>3.88</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>122</v>
+        <v>123</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>9.92</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44837.55208333334</v>
+        <v>44838.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>49.5</v>
+        <v>53.9</v>
       </c>
       <c r="I11" t="n">
         <v>50.73905431250435</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.75</v>
+        <v>-10.79</v>
       </c>
       <c r="L11" t="n">
-        <v>5.34</v>
+        <v>11.31</v>
       </c>
       <c r="M11" t="n">
-        <v>2.26</v>
+        <v>3.43</v>
       </c>
       <c r="N11" t="n">
-        <v>4.49</v>
+        <v>7.68</v>
       </c>
       <c r="O11" t="n">
         <v>-3.75</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>12.23</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44916.38541666666</v>
+        <v>44916.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>60.25</v>
+        <v>58.85</v>
       </c>
       <c r="I12" t="n">
         <v>60.08655615738239</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>78</v>
+        <v>78.16666666666667</v>
       </c>
       <c r="K12" t="n">
-        <v>11.78</v>
+        <v>9.18</v>
       </c>
       <c r="L12" t="n">
         <v>5.38</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>106</v>
+        <v>107</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>7.87</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44924.55208333334</v>
+        <v>44925.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>57.35</v>
+        <v>58.55</v>
       </c>
       <c r="I13" t="n">
         <v>57.91971238830738</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K13" t="n">
-        <v>2.55</v>
+        <v>0.51</v>
       </c>
       <c r="L13" t="n">
         <v>2.46</v>
@@ -1191,7 +1346,19 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,28 +1385,28 @@
         <v>8.4</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44950.55208333334</v>
+        <v>44951.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>58.65</v>
+        <v>57.45</v>
       </c>
       <c r="I14" t="n">
         <v>57.75474409480096</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K14" t="n">
-        <v>0.17</v>
+        <v>-1.88</v>
       </c>
       <c r="L14" t="n">
-        <v>2.31</v>
+        <v>2.82</v>
       </c>
       <c r="M14" t="n">
         <v>0.68</v>
       </c>
       <c r="N14" t="n">
-        <v>2.15</v>
+        <v>2.64</v>
       </c>
       <c r="O14" t="n">
         <v>2.7</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>6.26</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44959.38541666666</v>
+        <v>44959.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>58.8</v>
+        <v>59.65</v>
       </c>
       <c r="I15" t="n">
         <v>59.43369494659642</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.35</v>
+        <v>-3.83</v>
       </c>
       <c r="L15" t="n">
-        <v>4</v>
+        <v>4.09</v>
       </c>
       <c r="M15" t="n">
         <v>4.52</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>11.13</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44977.38541666666</v>
+        <v>44977.55208333334</v>
       </c>
       <c r="H16" t="n">
-        <v>55.45</v>
+        <v>54.9</v>
       </c>
       <c r="I16" t="n">
         <v>55.33693499159578</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>17.83333333333333</v>
+        <v>18</v>
       </c>
       <c r="K16" t="n">
-        <v>-7.04</v>
+        <v>-7.96</v>
       </c>
       <c r="L16" t="n">
-        <v>7.8</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="M16" t="n">
         <v>0.67</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>5.51</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44987.55208333334</v>
+        <v>44988.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>55.15</v>
+        <v>56.55</v>
       </c>
       <c r="I17" t="n">
         <v>56.23558620267487</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.46</v>
+        <v>-3.01</v>
       </c>
       <c r="L17" t="n">
-        <v>2.82</v>
+        <v>3.19</v>
       </c>
       <c r="M17" t="n">
-        <v>0.46</v>
+        <v>0.82</v>
       </c>
       <c r="N17" t="n">
-        <v>1.47</v>
+        <v>2.18</v>
       </c>
       <c r="O17" t="n">
         <v>-1.61</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>5.5</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44998.38541666666</v>
+        <v>44998.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>55.25</v>
+        <v>54.8</v>
       </c>
       <c r="I18" t="n">
         <v>54.91508450354029</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.3</v>
+        <v>-3.09</v>
       </c>
       <c r="L18" t="n">
-        <v>2.48</v>
+        <v>3.54</v>
       </c>
       <c r="M18" t="n">
         <v>0.44</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>4.87</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45019.38541666666</v>
+        <v>45019.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>55.45</v>
+        <v>55.6</v>
       </c>
       <c r="I19" t="n">
         <v>55.54240058508594</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>20.83333333333333</v>
+        <v>21</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.19</v>
+        <v>-1.46</v>
       </c>
       <c r="L19" t="n">
         <v>3.28</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>5.16</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45100.38541666666</v>
+        <v>45100.55208333334</v>
       </c>
       <c r="H20" t="n">
-        <v>78.05</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="I20" t="n">
         <v>77.84705497386626</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>80.83333333333333</v>
+        <v>81</v>
       </c>
       <c r="K20" t="n">
-        <v>40.38</v>
+        <v>39.66</v>
       </c>
       <c r="L20" t="n">
         <v>4.05</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>7.92</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45118.55208333334</v>
+        <v>45119.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>83</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I21" t="n">
         <v>83.21814960911929</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K21" t="n">
-        <v>-6.89</v>
+        <v>-7.66</v>
       </c>
       <c r="L21" t="n">
-        <v>6.89</v>
+        <v>8.69</v>
       </c>
       <c r="M21" t="n">
         <v>1.22</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>5.52</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45181.55208333334</v>
+        <v>45182.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>93.5</v>
+        <v>91.65000000000001</v>
       </c>
       <c r="I22" t="n">
         <v>92.06469948191339</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>62.16666666666666</v>
+        <v>63</v>
       </c>
       <c r="K22" t="n">
-        <v>11.84</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="L22" t="n">
         <v>3.65</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>88</v>
+        <v>89</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>7.32</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45243.55208333334</v>
+        <v>45245.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>86.15000000000001</v>
+        <v>87</v>
       </c>
       <c r="I23" t="n">
         <v>86.37702814432997</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>61.16666666666666</v>
+        <v>63</v>
       </c>
       <c r="K23" t="n">
-        <v>6</v>
+        <v>5.07</v>
       </c>
       <c r="L23" t="n">
         <v>7.36</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>3.64</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45246.55208333334</v>
+        <v>45247.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>88.65000000000001</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="I24" t="n">
         <v>85.17430288067767</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K24" t="n">
-        <v>1.9</v>
+        <v>-2.18</v>
       </c>
       <c r="L24" t="n">
-        <v>0.46</v>
+        <v>2.64</v>
       </c>
       <c r="M24" t="n">
-        <v>-0</v>
+        <v>1.86</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="O24" t="n">
         <v>0.7</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,25 +2144,25 @@
         <v>5.69</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45261.55208333334</v>
+        <v>45264.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>86.05</v>
+        <v>87.59999999999999</v>
       </c>
       <c r="I25" t="n">
         <v>86.33662743075972</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.12</v>
+        <v>-2.94</v>
       </c>
       <c r="L25" t="n">
-        <v>2.23</v>
+        <v>3.23</v>
       </c>
       <c r="M25" t="n">
-        <v>0.41</v>
+        <v>1.34</v>
       </c>
       <c r="N25" t="n">
         <v>1.42</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>4.41</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>89.75</v>
+        <v>87</v>
       </c>
       <c r="I26" t="n">
         <v>87.37881131623183</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K26" t="n">
-        <v>2.45</v>
+        <v>-0.68</v>
       </c>
       <c r="L26" t="n">
         <v>1.83</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>6.46</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45302.55208333334</v>
+        <v>45303.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>86.59999999999999</v>
+        <v>87.65000000000001</v>
       </c>
       <c r="I27" t="n">
         <v>87.238227090807</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>0.46</v>
+        <v>-0.75</v>
       </c>
       <c r="L27" t="n">
         <v>3.33</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>5.51</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45311.55208333334</v>
+        <v>45314.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>87.8</v>
+        <v>82</v>
       </c>
       <c r="I28" t="n">
         <v>83.8132403515115</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K28" t="n">
-        <v>0.17</v>
+        <v>-6.45</v>
       </c>
       <c r="L28" t="n">
-        <v>3.65</v>
+        <v>6.85</v>
       </c>
       <c r="M28" t="n">
-        <v>1.07</v>
+        <v>2.96</v>
       </c>
       <c r="N28" t="n">
-        <v>3.51</v>
+        <v>6.66</v>
       </c>
       <c r="O28" t="n">
         <v>0.6899999999999999</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>9.460000000000001</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45337.55208333334</v>
+        <v>45338.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>81.3</v>
+        <v>83.3</v>
       </c>
       <c r="I29" t="n">
         <v>83.16403302857036</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K29" t="n">
-        <v>0.85</v>
+        <v>-1.59</v>
       </c>
       <c r="L29" t="n">
         <v>3.9</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>6.4</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45362.55208333334</v>
+        <v>45363.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>80.45</v>
+        <v>79.65000000000001</v>
       </c>
       <c r="I30" t="n">
         <v>80.14845869696769</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.42</v>
+        <v>-4.38</v>
       </c>
       <c r="L30" t="n">
         <v>4.8</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>5.5</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45385.55208333334</v>
+        <v>45386.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>78.3</v>
+        <v>79.45</v>
       </c>
       <c r="I31" t="n">
         <v>79.39268091017351</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K31" t="n">
-        <v>1.69</v>
+        <v>0.25</v>
       </c>
       <c r="L31" t="n">
         <v>1.95</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>4.79</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45408.55208333334</v>
+        <v>45411.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>84.7</v>
+        <v>81.25</v>
       </c>
       <c r="I32" t="n">
         <v>81.53648202724338</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K32" t="n">
-        <v>6.61</v>
+        <v>2.27</v>
       </c>
       <c r="L32" t="n">
         <v>1.13</v>
@@ -2265,7 +2648,7 @@
         <v>1.54</v>
       </c>
       <c r="N32" t="n">
-        <v>2.02</v>
+        <v>3.72</v>
       </c>
       <c r="O32" t="n">
         <v>1.66</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>6.3</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45457.55208333334</v>
+        <v>45461.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>78.12</v>
+        <v>81.13</v>
       </c>
       <c r="I33" t="n">
         <v>78.93140482157139</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K33" t="n">
-        <v>3.85</v>
+        <v>0.15</v>
       </c>
       <c r="L33" t="n">
         <v>2.77</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>6.79</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45474.55208333334</v>
+        <v>45475.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>81.15000000000001</v>
+        <v>78.75</v>
       </c>
       <c r="I34" t="n">
         <v>79.4445402153563</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K34" t="n">
-        <v>0.02</v>
+        <v>-2.93</v>
       </c>
       <c r="L34" t="n">
         <v>3.86</v>
@@ -2379,7 +2786,7 @@
         <v>0.35</v>
       </c>
       <c r="N34" t="n">
-        <v>1.18</v>
+        <v>2.54</v>
       </c>
       <c r="O34" t="n">
         <v>4.16</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>6.21</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45525.38541666666</v>
+        <v>45525.55208333334</v>
       </c>
       <c r="H35" t="n">
-        <v>73.3</v>
+        <v>73.91</v>
       </c>
       <c r="I35" t="n">
         <v>73.65762754885442</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>50</v>
+        <v>50.16666666666666</v>
       </c>
       <c r="K35" t="n">
-        <v>6.92</v>
+        <v>6.15</v>
       </c>
       <c r="L35" t="n">
         <v>4.25</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>4.28</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45544.38541666666</v>
+        <v>45544.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>73.65000000000001</v>
+        <v>72.34999999999999</v>
       </c>
       <c r="I36" t="n">
         <v>72.49240362353214</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>18.83333333333333</v>
+        <v>19</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.35</v>
+        <v>-2.11</v>
       </c>
       <c r="L36" t="n">
-        <v>1.46</v>
+        <v>2.45</v>
       </c>
       <c r="M36" t="n">
         <v>2.71</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,25 +2972,25 @@
         <v>5.49</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45562.55208333334</v>
+        <v>45565.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>74.19</v>
+        <v>74.73</v>
       </c>
       <c r="I37" t="n">
         <v>74.70832245488425</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>18</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.54</v>
+        <v>-3.29</v>
       </c>
       <c r="L37" t="n">
-        <v>3.52</v>
+        <v>5.14</v>
       </c>
       <c r="M37" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="N37" t="n">
         <v>1.9</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>4.23</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45569.55208333334</v>
+        <v>45572.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>72</v>
+        <v>71.47</v>
       </c>
       <c r="I38" t="n">
         <v>71.56855604595823</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K38" t="n">
-        <v>-3.65</v>
+        <v>-4.36</v>
       </c>
       <c r="L38" t="n">
-        <v>4.66</v>
+        <v>5.78</v>
       </c>
       <c r="M38" t="n">
         <v>0.95</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>5.42</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45594.55208333334</v>
+        <v>45595.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>67.56</v>
+        <v>69.01000000000001</v>
       </c>
       <c r="I39" t="n">
         <v>67.70708461079285</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K39" t="n">
-        <v>5.47</v>
+        <v>3.44</v>
       </c>
       <c r="L39" t="n">
         <v>3.18</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,25 +3179,25 @@
         <v>8.99</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45609.55208333334</v>
+        <v>45610.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>64.27</v>
+        <v>63.38</v>
       </c>
       <c r="I40" t="n">
         <v>63.68660730817293</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K40" t="n">
-        <v>-6.87</v>
+        <v>-8.16</v>
       </c>
       <c r="L40" t="n">
         <v>8.56</v>
       </c>
       <c r="M40" t="n">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="N40" t="n">
         <v>3.93</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>7.3</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45660.38541666666</v>
+        <v>45660.55208333334</v>
       </c>
       <c r="H41" t="n">
-        <v>64.78</v>
+        <v>65.5</v>
       </c>
       <c r="I41" t="n">
         <v>64.86321762081946</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>50</v>
+        <v>50.16666666666666</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.21</v>
+        <v>-3.34</v>
       </c>
       <c r="L41" t="n">
         <v>5.06</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>5.45</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45664.55208333334</v>
+        <v>45665.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>62.42</v>
+        <v>61.66</v>
       </c>
       <c r="I42" t="n">
         <v>61.92983367652423</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>4</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K42" t="n">
-        <v>-4.7</v>
+        <v>-5.86</v>
       </c>
       <c r="L42" t="n">
-        <v>4.89</v>
+        <v>6.05</v>
       </c>
       <c r="M42" t="n">
         <v>0.02</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>6.3</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45672.55208333334</v>
+        <v>45673.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>62.14</v>
+        <v>63.06</v>
       </c>
       <c r="I43" t="n">
         <v>62.83046527062089</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.78</v>
+        <v>-2.27</v>
       </c>
       <c r="L43" t="n">
-        <v>2.66</v>
+        <v>2.79</v>
       </c>
       <c r="M43" t="n">
         <v>1.1</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>5.76</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45681.55208333334</v>
+        <v>45684.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>62.17</v>
+        <v>57.63</v>
       </c>
       <c r="I44" t="n">
         <v>60.63709739485019</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.41</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>2.39</v>
+        <v>8.98</v>
       </c>
       <c r="M44" t="n">
-        <v>0.38</v>
+        <v>5.08</v>
       </c>
       <c r="N44" t="n">
-        <v>1.16</v>
+        <v>8.51</v>
       </c>
       <c r="O44" t="n">
         <v>0.8</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>10.37</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45687.55208333334</v>
+        <v>45688.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>61.1</v>
+        <v>62.54</v>
       </c>
       <c r="I45" t="n">
         <v>61.80870202954787</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K45" t="n">
-        <v>-6.02</v>
+        <v>-8.52</v>
       </c>
       <c r="L45" t="n">
-        <v>7.41</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="M45" t="n">
         <v>1.62</v>
       </c>
       <c r="N45" t="n">
-        <v>2.88</v>
+        <v>3.58</v>
       </c>
       <c r="O45" t="n">
         <v>-8.51</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45701.55208333334</v>
+        <v>45702.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>61.5</v>
+        <v>60.01</v>
       </c>
       <c r="I46" t="n">
         <v>60.84703944446174</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.66</v>
+        <v>-4.05</v>
       </c>
       <c r="L46" t="n">
-        <v>3.73</v>
+        <v>4.17</v>
       </c>
       <c r="M46" t="n">
         <v>0.85</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>7.6</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45735.55208333334</v>
+        <v>45736.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>55.4</v>
+        <v>56.09</v>
       </c>
       <c r="I47" t="n">
         <v>55.68892848142647</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K47" t="n">
-        <v>7.68</v>
+        <v>6.53</v>
       </c>
       <c r="L47" t="n">
         <v>3.07</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>5.4</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45744.38541666666</v>
+        <v>45744.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>55.38</v>
+        <v>54.86</v>
       </c>
       <c r="I48" t="n">
         <v>55.15011386014626</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K48" t="n">
-        <v>-1.27</v>
+        <v>-2.19</v>
       </c>
       <c r="L48" t="n">
-        <v>1.28</v>
+        <v>2.6</v>
       </c>
       <c r="M48" t="n">
         <v>0.19</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,28 +3800,28 @@
         <v>6.15</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45748.55208333334</v>
+        <v>45750.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>57.2</v>
+        <v>59.49</v>
       </c>
       <c r="I49" t="n">
         <v>58.23238244064051</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>4</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K49" t="n">
-        <v>-4.27</v>
+        <v>-8.44</v>
       </c>
       <c r="L49" t="n">
-        <v>5.1</v>
+        <v>9</v>
       </c>
       <c r="M49" t="n">
         <v>0.35</v>
       </c>
       <c r="N49" t="n">
-        <v>4.27</v>
+        <v>5.54</v>
       </c>
       <c r="O49" t="n">
         <v>-2.61</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,25 +3869,25 @@
         <v>8.859999999999999</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>57.8</v>
+        <v>55.78</v>
       </c>
       <c r="I50" t="n">
         <v>56.04489088069576</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K50" t="n">
-        <v>-2.84</v>
+        <v>-6.24</v>
       </c>
       <c r="L50" t="n">
-        <v>4.44</v>
+        <v>11.82</v>
       </c>
       <c r="M50" t="n">
-        <v>0.35</v>
+        <v>7.87</v>
       </c>
       <c r="N50" t="n">
         <v>4.26</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,25 +3938,25 @@
         <v>7.48</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45756.55208333334</v>
+        <v>45758.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>59.29</v>
+        <v>60.16</v>
       </c>
       <c r="I51" t="n">
         <v>59.95100954797279</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K51" t="n">
-        <v>-6.29</v>
+        <v>-7.85</v>
       </c>
       <c r="L51" t="n">
-        <v>6.74</v>
+        <v>8.32</v>
       </c>
       <c r="M51" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="N51" t="n">
         <v>2.56</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45848.55208333334</v>
+        <v>45849.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>76.59</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="I52" t="n">
         <v>75.22487230967364</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>90.16666666666667</v>
+        <v>91</v>
       </c>
       <c r="K52" t="n">
-        <v>27.31</v>
+        <v>24.92</v>
       </c>
       <c r="L52" t="n">
         <v>1.38</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>4</v>
+      </c>
+      <c r="U52" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>4.58</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45887.55208333334</v>
+        <v>45888.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>69.93000000000001</v>
+        <v>70.77</v>
       </c>
       <c r="I53" t="n">
         <v>70.7500954457596</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>38.16666666666666</v>
+        <v>39</v>
       </c>
       <c r="K53" t="n">
-        <v>6.95</v>
+        <v>5.83</v>
       </c>
       <c r="L53" t="n">
         <v>2.05</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>4.81</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45897.38541666666</v>
+        <v>45897.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>68.73999999999999</v>
+        <v>68.33</v>
       </c>
       <c r="I54" t="n">
         <v>68.66590106023764</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K54" t="n">
-        <v>-2.87</v>
+        <v>-3.45</v>
       </c>
       <c r="L54" t="n">
-        <v>3.59</v>
+        <v>4.06</v>
       </c>
       <c r="M54" t="n">
         <v>0.52</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>4.02</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45903.55208333334</v>
+        <v>45904.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>70.51000000000001</v>
+        <v>71.69</v>
       </c>
       <c r="I55" t="n">
         <v>71.02907924346549</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K55" t="n">
-        <v>-3.19</v>
+        <v>-4.92</v>
       </c>
       <c r="L55" t="n">
-        <v>3.5</v>
+        <v>4.98</v>
       </c>
       <c r="M55" t="n">
-        <v>0.04</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N55" t="n">
-        <v>1.54</v>
+        <v>2.54</v>
       </c>
       <c r="O55" t="n">
         <v>-0.5</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.09</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45923.38541666666</v>
+        <v>45923.55208333334</v>
       </c>
       <c r="H56" t="n">
-        <v>70.84</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I56" t="n">
         <v>70.66690459945848</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>19</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="K56" t="n">
-        <v>-1.19</v>
+        <v>-1.52</v>
       </c>
       <c r="L56" t="n">
         <v>1.84</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>3.34</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45933.55208333334</v>
+        <v>45936.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>69.15000000000001</v>
+        <v>71.04000000000001</v>
       </c>
       <c r="I57" t="n">
         <v>70.85614830759057</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>10</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K57" t="n">
-        <v>2.05</v>
+        <v>-0.62</v>
       </c>
       <c r="L57" t="n">
         <v>1.01</v>
@@ -3690,7 +4373,7 @@
         <v>0.35</v>
       </c>
       <c r="N57" t="n">
-        <v>1.51</v>
+        <v>2.82</v>
       </c>
       <c r="O57" t="n">
         <v>-0.48</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>5.33</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45985.38541666666</v>
+        <v>45985.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>78.48</v>
+        <v>77.63</v>
       </c>
       <c r="I58" t="n">
         <v>78.14247950786017</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>49</v>
+        <v>49.16666666666666</v>
       </c>
       <c r="K58" t="n">
-        <v>10.47</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="L58" t="n">
         <v>2.79</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>66</v>
+        <v>67</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>4.6</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45992.55208333334</v>
+        <v>45993.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>80.59999999999999</v>
+        <v>82.17</v>
       </c>
       <c r="I59" t="n">
         <v>81.19871499467379</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K59" t="n">
-        <v>-3.83</v>
+        <v>-5.85</v>
       </c>
       <c r="L59" t="n">
-        <v>4.73</v>
+        <v>5.99</v>
       </c>
       <c r="M59" t="n">
         <v>0.35</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>4.67</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45996.55208333334</v>
+        <v>45999.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>80.86</v>
+        <v>79.03</v>
       </c>
       <c r="I60" t="n">
         <v>79.16976788511586</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K60" t="n">
-        <v>-1.59</v>
+        <v>-3.82</v>
       </c>
       <c r="L60" t="n">
-        <v>3.1</v>
+        <v>3.97</v>
       </c>
       <c r="M60" t="n">
         <v>0.36</v>
       </c>
       <c r="N60" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="O60" t="n">
         <v>1.71</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>6.16</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46003.55208333334</v>
+        <v>46006.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>82.25</v>
+        <v>84.28</v>
       </c>
       <c r="I61" t="n">
         <v>82.43893414779657</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K61" t="n">
-        <v>-4.07</v>
+        <v>-6.64</v>
       </c>
       <c r="L61" t="n">
-        <v>4.8</v>
+        <v>6.83</v>
       </c>
       <c r="M61" t="n">
         <v>0.14</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>6.01</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46034.55208333334</v>
+        <v>46035.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>84.89</v>
+        <v>82.56</v>
       </c>
       <c r="I62" t="n">
         <v>83.30384381215276</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K62" t="n">
-        <v>0.72</v>
+        <v>-2.04</v>
       </c>
       <c r="L62" t="n">
         <v>3.01</v>
@@ -3975,7 +4718,7 @@
         <v>0.57</v>
       </c>
       <c r="N62" t="n">
-        <v>1.29</v>
+        <v>2.24</v>
       </c>
       <c r="O62" t="n">
         <v>1.91</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>6.97</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46071.38541666666</v>
+        <v>46071.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>83.22</v>
+        <v>85.34999999999999</v>
       </c>
       <c r="I63" t="n">
         <v>84.92851638604654</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>36</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.8</v>
+        <v>-3.38</v>
       </c>
       <c r="L63" t="n">
         <v>4.14</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,28 +4835,28 @@
         <v>5.68</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46073.55208333334</v>
+        <v>46076.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>83.25</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="I64" t="n">
         <v>80.82569911005928</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>2</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.46</v>
+        <v>-17.7</v>
       </c>
       <c r="L64" t="n">
-        <v>3.63</v>
+        <v>21.73</v>
       </c>
       <c r="M64" t="n">
-        <v>0.48</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="N64" t="n">
-        <v>3.22</v>
+        <v>15.86</v>
       </c>
       <c r="O64" t="n">
         <v>2.84</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>13.43</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>61.17</v>
+        <v>65.05</v>
       </c>
       <c r="I65" t="n">
         <v>63.39084697762109</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K65" t="n">
-        <v>12.91</v>
+        <v>7.39</v>
       </c>
       <c r="L65" t="n">
         <v>7</v>
       </c>
       <c r="M65" t="n">
-        <v>3.38</v>
+        <v>4.61</v>
       </c>
       <c r="N65" t="n">
-        <v>3.68</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="O65" t="n">
         <v>-15.86</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>9.140000000000001</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46157.55208333334</v>
+        <v>46160.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>67.68000000000001</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="I66" t="n">
         <v>67.42971551081645</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K66" t="n">
-        <v>4.04</v>
+        <v>3.32</v>
       </c>
       <c r="L66" t="n">
         <v>3.15</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,22 +5042,22 @@
         <v>5.24</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46169.38541666666</v>
+        <v>46169.55208333334</v>
       </c>
       <c r="H67" t="n">
-        <v>70.43000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I67" t="n">
         <v>70.72874648662297</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K67" t="n">
-        <v>-4.79</v>
+        <v>-6.98</v>
       </c>
       <c r="L67" t="n">
-        <v>5.53</v>
+        <v>7.65</v>
       </c>
       <c r="M67" t="n">
         <v>0.9399999999999999</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>5.08</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46261.38541666666</v>
+        <v>46261.55208333334</v>
       </c>
       <c r="H68" t="n">
-        <v>84.31</v>
+        <v>83.78</v>
       </c>
       <c r="I68" t="n">
         <v>84.23010493167995</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>91.83333333333333</v>
+        <v>92</v>
       </c>
       <c r="K68" t="n">
-        <v>17.26</v>
+        <v>16.52</v>
       </c>
       <c r="L68" t="n">
         <v>3.3</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>128</v>
+        <v>129</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>4</v>
+      </c>
+      <c r="U68" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>3.17</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46267.55208333334</v>
+        <v>46268.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>84.95</v>
+        <v>86.53</v>
       </c>
       <c r="I69" t="n">
         <v>85.58853336505392</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K69" t="n">
-        <v>-1.4</v>
+        <v>-3.28</v>
       </c>
       <c r="L69" t="n">
-        <v>1.75</v>
+        <v>4.2</v>
       </c>
       <c r="M69" t="n">
         <v>1.08</v>
       </c>
       <c r="N69" t="n">
-        <v>1.04</v>
+        <v>2.88</v>
       </c>
       <c r="O69" t="n">
         <v>-1.12</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S69" t="b">
+        <v>0</v>
+      </c>
+      <c r="T69" t="n">
+        <v>1</v>
+      </c>
+      <c r="U69" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>3.94</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46289.38541666666</v>
+        <v>46289.55208333334</v>
       </c>
       <c r="H70" t="n">
-        <v>84.5</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="I70" t="n">
         <v>84.20546161765178</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>21</v>
+        <v>21.16666666666667</v>
       </c>
       <c r="K70" t="n">
-        <v>-2.35</v>
+        <v>-3.39</v>
       </c>
       <c r="L70" t="n">
-        <v>2.69</v>
+        <v>3.73</v>
       </c>
       <c r="M70" t="n">
         <v>3.86</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4491,6 +5342,14 @@
       <c r="Q71" t="n">
         <v>43</v>
       </c>
+      <c r="R71" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6593,7 +7452,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.7</v>
+        <v>24.9</v>
       </c>
     </row>
     <row r="6">
@@ -6603,7 +7462,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7">
@@ -6613,7 +7472,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>91.8</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8">
@@ -6623,7 +7482,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6633,7 +7492,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>33.2</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -6643,7 +7502,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52.2</v>
+        <v>52.7</v>
       </c>
     </row>
     <row r="11">
@@ -6683,7 +7542,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.41</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="15">
@@ -6693,7 +7552,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.75</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="16">
@@ -6703,7 +7562,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.04</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="17">
@@ -6713,7 +7572,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>57.14</v>
+        <v>51.09</v>
       </c>
     </row>
     <row r="18">
@@ -6723,7 +7582,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>43.5</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="19">
@@ -6733,7 +7592,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.74</v>
+        <v>4.92</v>
       </c>
     </row>
     <row r="20">
@@ -6743,7 +7602,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.59</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="21">
@@ -6753,7 +7612,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8.56</v>
+        <v>21.73</v>
       </c>
     </row>
     <row r="22">
@@ -6763,7 +7622,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23">
@@ -6773,7 +7632,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -6783,7 +7642,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.39</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="25">
@@ -6793,7 +7652,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.29</v>
+        <v>9.720000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -6803,7 +7662,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.95</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="27">
@@ -6813,7 +7672,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.11</v>
+        <v>15.86</v>
       </c>
     </row>
     <row r="28">
@@ -6823,7 +7682,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
